--- a/compare_information.xlsx
+++ b/compare_information.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL\MP List Check Tool_v4.1_20250409\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v4.3_20250721\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085CB98C-FB0E-41CC-89E7-4971DD4556D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2B603F-9409-4E72-90EF-AB5EB235F50E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="181">
   <si>
     <t>IC</t>
   </si>
@@ -675,12 +676,55 @@
     <t>INX6.78</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>V1.0.1.31_20250429</t>
+  </si>
+  <si>
+    <t>CSOT6.76</t>
+  </si>
+  <si>
+    <t>BOE4.95</t>
+  </si>
+  <si>
+    <t>MDT5.99</t>
+  </si>
+  <si>
+    <t>MDT6.82</t>
+  </si>
+  <si>
+    <t>BOE4.96</t>
+  </si>
+  <si>
+    <t>CTC5.45</t>
+  </si>
+  <si>
+    <t>BOE5.46</t>
+  </si>
+  <si>
+    <t>AL6780-676</t>
+  </si>
+  <si>
+    <t>AL6780-FHD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AL6780</t>
+  </si>
+  <si>
+    <t>CTC6.56HD05A</t>
+  </si>
+  <si>
+    <t>CSOT6.88_BM6880LT1-1</t>
+  </si>
+  <si>
+    <t>V1.0.1.31_20250402</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -740,6 +784,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -767,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -790,6 +840,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1070,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1098,11 +1151,11 @@
       <c r="F1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
@@ -1120,9 +1173,9 @@
       <c r="F2" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -1140,9 +1193,9 @@
       <c r="F3" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1160,9 +1213,9 @@
       <c r="F4" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1180,9 +1233,9 @@
       <c r="F5" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1200,9 +1253,9 @@
       <c r="F6" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -1222,7 +1275,9 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2">
+        <v>7302</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1307,6 +1362,12 @@
       <c r="C13" s="5" t="s">
         <v>111</v>
       </c>
+      <c r="E13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
@@ -1316,6 +1377,12 @@
       <c r="C14" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="E14" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
@@ -1325,6 +1392,7 @@
       <c r="C15" s="5" t="s">
         <v>129</v>
       </c>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1701,14 +1769,18 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="C56" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="C57" s="5" t="s">
         <v>81</v>
       </c>
@@ -1871,6 +1943,56 @@
     <row r="82" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C82" s="5" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C87" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C90" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1881,4 +2003,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7070EE51-A697-4C75-BD73-06572F75A4CC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/compare_information.xlsx
+++ b/compare_information.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v4.4_20250724\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v4.5_20251020\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD96E146-7A8D-4154-B784-CD4FF76A36BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B463AC-32D2-46FC-9EDC-F379373F53C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="268">
   <si>
     <t>IC</t>
   </si>
@@ -32,15 +32,6 @@
     <t>玻璃</t>
   </si>
   <si>
-    <t>需统一的项目号</t>
-  </si>
-  <si>
-    <t>统一后的项目名称</t>
-  </si>
-  <si>
-    <t>PS：“需统一项目号”即为使用同一个序号但是项目号有备注或有差异的项目，因序号检验逻辑为以项目号为基准，需将这些项目号统一</t>
-  </si>
-  <si>
     <t>V1.0.0.8_20220309</t>
   </si>
   <si>
@@ -98,6 +89,9 @@
     <t>PANDA6.517</t>
   </si>
   <si>
+    <t>7272CA</t>
+  </si>
+  <si>
     <t>V1.0.1.5_20230213</t>
   </si>
   <si>
@@ -494,6 +488,18 @@
     <t>CSOT6.88_BM6880LT1-1</t>
   </si>
   <si>
+    <t>HKC6.56_4-1</t>
+  </si>
+  <si>
+    <t>CTC6.95</t>
+  </si>
+  <si>
+    <t>TM4.96</t>
+  </si>
+  <si>
+    <t>BOE6.88</t>
+  </si>
+  <si>
     <t>Module</t>
   </si>
   <si>
@@ -789,13 +795,50 @@
   </si>
   <si>
     <t>宏凯</t>
+  </si>
+  <si>
+    <t>华佳</t>
+  </si>
+  <si>
+    <t>美力凯</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>G1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDT6.088_MLAG061WF12A(C)</t>
+  </si>
+  <si>
+    <t>V1.0.1.32_20251110</t>
+  </si>
+  <si>
+    <t>7202MA</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>7202MA</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>联信康</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>整机代码</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>模组物料</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -828,38 +871,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -889,7 +920,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -910,7 +941,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -918,13 +948,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1200,19 +1232,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="11" customWidth="1"/>
-    <col min="2" max="2" width="24.625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="22.5" style="11" customWidth="1"/>
-    <col min="4" max="4" width="21.5" style="11" customWidth="1"/>
-    <col min="5" max="5" width="23.625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="27.25" style="11" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="14" style="10" customWidth="1"/>
+    <col min="2" max="2" width="24.625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="22.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="10" customWidth="1"/>
+    <col min="5" max="5" width="23.625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="27.25" style="10" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1222,793 +1254,784 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-    </row>
-    <row r="2" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>7272</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7302</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
-      <c r="B58" s="3"/>
+      <c r="B58" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="C58" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="C74" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="C75" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="C76" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C77" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C78" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C79" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C80" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C81" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C82" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C83" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C84" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C85" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="86" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C86" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C87" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C88" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C89" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C90" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C91" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C92" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C93" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C94" s="5" t="s">
         <v>156</v>
       </c>
     </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C95" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C96" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C97" s="10" t="s">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G1:I6"/>
-  </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2017,158 +2040,167 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>162</v>
       </c>
+      <c r="F1" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="12">
         <v>7272</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
+      <c r="A3" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
+      <c r="A4" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="12">
         <v>7302</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>190</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="F6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
+        <v>263</v>
+      </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F8" t="s">
         <v>2</v>
@@ -2176,287 +2208,309 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>203</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>205</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C13" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>255</v>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B62" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B63" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/compare_information.xlsx
+++ b/compare_information.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v4.5_20251020\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v5.1_20260104\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B463AC-32D2-46FC-9EDC-F379373F53C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67252F23-D2BD-44E5-A9BE-D4006A39FF27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="262">
   <si>
     <t>IC</t>
   </si>
@@ -185,9 +185,6 @@
     <t>V1.0.1.10_20230629</t>
   </si>
   <si>
-    <t>BOE6.517_BV065</t>
-  </si>
-  <si>
     <t>V1.0.1.13_20230719</t>
   </si>
   <si>
@@ -245,15 +242,9 @@
     <t>V1.0.1.17_20230914</t>
   </si>
   <si>
-    <t>INX6.56_A20</t>
-  </si>
-  <si>
     <t>V1.0.1.17_20230921</t>
   </si>
   <si>
-    <t>INX6.56_A18</t>
-  </si>
-  <si>
     <t>V1.0.1.17_20230921_8</t>
   </si>
   <si>
@@ -311,9 +302,6 @@
     <t>V1.0.1.23_20231226</t>
   </si>
   <si>
-    <t>CTC6.56_Qhd</t>
-  </si>
-  <si>
     <t>V1.0.1.24_20240119</t>
   </si>
   <si>
@@ -347,9 +335,6 @@
     <t>V1.0.1.27_20240822</t>
   </si>
   <si>
-    <t>CTC6.56_HD03A</t>
-  </si>
-  <si>
     <t>V1.0.1.28_20241018</t>
   </si>
   <si>
@@ -392,9 +377,6 @@
     <t>CTC6.88</t>
   </si>
   <si>
-    <t>CTC6.56_HD05A</t>
-  </si>
-  <si>
     <t>CSOT6.56</t>
   </si>
   <si>
@@ -413,9 +395,6 @@
     <t>BOE5.7</t>
   </si>
   <si>
-    <t>BOE6.517_BS065</t>
-  </si>
-  <si>
     <t>IVO6.75</t>
   </si>
   <si>
@@ -434,21 +413,6 @@
     <t>HKC6.56 3-1</t>
   </si>
   <si>
-    <t>sharp6.745</t>
-  </si>
-  <si>
-    <t>sharp6.517</t>
-  </si>
-  <si>
-    <t>sharp6.72</t>
-  </si>
-  <si>
-    <t>CTC6.56_qHD</t>
-  </si>
-  <si>
-    <t>MDT6.517B版</t>
-  </si>
-  <si>
     <t>CSOT6.88</t>
   </si>
   <si>
@@ -480,15 +444,6 @@
   </si>
   <si>
     <t>BOE4.96</t>
-  </si>
-  <si>
-    <t>CTC6.56HD05A</t>
-  </si>
-  <si>
-    <t>CSOT6.88_BM6880LT1-1</t>
-  </si>
-  <si>
-    <t>HKC6.56_4-1</t>
   </si>
   <si>
     <t>CTC6.95</t>
@@ -804,13 +759,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>G1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MDT6.088_MLAG061WF12A(C)</t>
-  </si>
-  <si>
     <t>V1.0.1.32_20251110</t>
   </si>
   <si>
@@ -826,11 +774,53 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>整机代码</t>
+    <t>模组物料</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>模组物料</t>
+    <t>2026年度</t>
+  </si>
+  <si>
+    <t>整机软件</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>整机干扰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TM6.67</t>
+  </si>
+  <si>
+    <t>BOE6.088</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTC6.56</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>INX6.56</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKC6.56</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDT6.088</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSOT6.88</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDT6.517B版</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.0.1.33_20251127</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1232,12 +1222,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" style="10" customWidth="1"/>
     <col min="2" max="2" width="24.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="22.5" style="10" customWidth="1"/>
+    <col min="3" max="3" width="33.375" style="10" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="10" customWidth="1"/>
     <col min="5" max="5" width="23.625" style="10" customWidth="1"/>
     <col min="6" max="6" width="27.25" style="10" customWidth="1"/>
@@ -1351,7 +1341,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>25</v>
@@ -1494,184 +1484,184 @@
         <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>72</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>92</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>94</v>
@@ -1680,7 +1670,7 @@
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>96</v>
@@ -1689,7 +1679,7 @@
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>98</v>
@@ -1698,7 +1688,7 @@
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>100</v>
@@ -1707,7 +1697,7 @@
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>102</v>
@@ -1716,320 +1706,287 @@
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>104</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
-      <c r="B59" s="3"/>
+      <c r="B59" s="7" t="s">
+        <v>261</v>
+      </c>
       <c r="C59" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="5" t="s">
-        <v>133</v>
+      <c r="C70" s="6" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="C74" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
-      <c r="C75" s="5" t="s">
-        <v>138</v>
+      <c r="C75" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="C76" s="5" t="s">
-        <v>139</v>
+      <c r="C76" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C77" s="6" t="s">
-        <v>140</v>
+      <c r="C77" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C78" s="6" t="s">
-        <v>141</v>
+      <c r="C78" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C79" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C80" s="5" t="s">
-        <v>143</v>
+      <c r="C80" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C81" s="5" t="s">
-        <v>144</v>
+      <c r="C81" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C82" s="5" t="s">
-        <v>145</v>
+        <v>259</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C83" t="s">
-        <v>146</v>
+      <c r="C83" s="5" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C84" t="s">
-        <v>147</v>
+      <c r="C84" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C85" t="s">
-        <v>148</v>
+      <c r="C85" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C86" t="s">
-        <v>149</v>
+      <c r="C86" s="5" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C87" s="5" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C88" t="s">
-        <v>151</v>
+      <c r="C88" s="10" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="89" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C89" t="s">
-        <v>152</v>
+      <c r="C89" s="5" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C90" s="5" t="s">
-        <v>121</v>
-      </c>
+      <c r="C90" s="5"/>
     </row>
     <row r="91" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C91" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C92" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C93" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C94" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C95" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C96" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C97" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C91" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2048,22 +2005,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -2071,22 +2028,22 @@
         <v>7272</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -2094,22 +2051,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -2117,22 +2074,22 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="G4" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2140,22 +2097,22 @@
         <v>7302</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F5" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G5" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2163,44 +2120,45 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>260</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E6" s="5"/>
       <c r="F6" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G6" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F7" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F8" t="s">
         <v>2</v>
@@ -2208,304 +2166,307 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>207</v>
+        <v>192</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C14" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B62" s="5" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B63" s="5" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/compare_information.xlsx
+++ b/compare_information.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v5.1_20260104\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v5.2_20260109\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67252F23-D2BD-44E5-A9BE-D4006A39FF27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F236C05D-2504-49F8-957F-12575D387197}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="272">
   <si>
     <t>IC</t>
   </si>
@@ -821,6 +821,46 @@
   </si>
   <si>
     <t>V1.0.1.33_20251127</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Publisher</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>kakarot</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>shangcong</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>xiuhui</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nico</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>shine</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>evan</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>peng</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TDDIRobot</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>兴邦达</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -883,7 +923,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -906,11 +946,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -946,6 +999,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1997,10 +2053,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -2022,8 +2081,11 @@
       <c r="G1" s="11" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>7272</v>
       </c>
@@ -2045,8 +2107,11 @@
       <c r="G2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>8</v>
       </c>
@@ -2068,8 +2133,11 @@
       <c r="G3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>5</v>
       </c>
@@ -2091,8 +2159,11 @@
       <c r="G4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>7302</v>
       </c>
@@ -2114,8 +2185,11 @@
       <c r="G5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>22</v>
       </c>
@@ -2135,8 +2209,11 @@
       <c r="G6" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>246</v>
       </c>
@@ -2152,8 +2229,11 @@
       <c r="G7" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>182</v>
       </c>
@@ -2163,8 +2243,11 @@
       <c r="F8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -2174,8 +2257,11 @@
       <c r="F9" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>187</v>
       </c>
@@ -2186,7 +2272,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>189</v>
       </c>
@@ -2197,7 +2283,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>191</v>
       </c>
@@ -2208,7 +2294,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>193</v>
       </c>
@@ -2216,7 +2302,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>195</v>
       </c>
@@ -2224,12 +2310,12 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>198</v>
       </c>
@@ -2467,6 +2553,11 @@
     <row r="63" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B63" s="5" t="s">
         <v>248</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B64" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/compare_information.xlsx
+++ b/compare_information.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -58,18 +58,18 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
       <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -138,12 +138,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -154,16 +148,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -513,16 +504,16 @@
   <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col width="14" customWidth="1" style="10" min="1" max="1"/>
-    <col width="24.625" customWidth="1" style="10" min="2" max="2"/>
-    <col width="33.375" customWidth="1" style="10" min="3" max="3"/>
-    <col width="21.5" customWidth="1" style="10" min="4" max="4"/>
-    <col width="23.625" customWidth="1" style="10" min="5" max="5"/>
-    <col width="27.25" customWidth="1" style="10" min="6" max="6"/>
-    <col width="18.625" customWidth="1" style="10" min="9" max="9"/>
+    <col width="14" customWidth="1" style="8" min="1" max="1"/>
+    <col width="24.625" customWidth="1" style="8" min="2" max="2"/>
+    <col width="33.375" customWidth="1" style="8" min="3" max="3"/>
+    <col width="21.5" customWidth="1" style="8" min="4" max="4"/>
+    <col width="23.625" customWidth="1" style="8" min="5" max="5"/>
+    <col width="27.25" customWidth="1" style="8" min="6" max="6"/>
+    <col width="18.625" customWidth="1" style="8" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="10">
+    <row r="1" ht="15.6" customHeight="1" s="8">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>IC</t>
@@ -539,7 +530,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.9" customHeight="1" s="10">
+    <row r="2" ht="13.9" customHeight="1" s="8">
       <c r="A2" s="2" t="n">
         <v>7272</v>
       </c>
@@ -554,8 +545,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="13.9" customHeight="1" s="10">
-      <c r="A3" s="17" t="inlineStr">
+    <row r="3" ht="13.9" customHeight="1" s="8">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>7202M</t>
         </is>
@@ -589,7 +580,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>7202H 7202M</t>
         </is>
@@ -606,7 +597,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>7202M 7202H</t>
         </is>
@@ -623,7 +614,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>7302B</t>
         </is>
@@ -639,7 +630,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="18" t="n"/>
+      <c r="F7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -656,10 +647,10 @@
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="18" t="n"/>
+      <c r="F8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>7272CA</t>
         </is>
@@ -675,10 +666,10 @@
         </is>
       </c>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="17" t="n"/>
+      <c r="F9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>7202MA</t>
         </is>
@@ -694,10 +685,12 @@
         </is>
       </c>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="17" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="2" t="n">
+        <v>7371</v>
+      </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>V1.0.1.5_20230228</t>
@@ -709,7 +702,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="17" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -724,7 +717,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="17" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -738,7 +731,7 @@
           <t>HKC6.517</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n"/>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -753,7 +746,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="9" t="n"/>
+      <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -767,7 +760,7 @@
           <t>HKC6.517 3-1</t>
         </is>
       </c>
-      <c r="F15" s="9" t="n"/>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1331,7 +1324,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>V1.0.1.33_20251127</t>
         </is>
@@ -1344,7 +1337,11 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
-      <c r="B60" s="3" t="n"/>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>V1.0.1.34_20260311</t>
+        </is>
+      </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
           <t>HKC6.67</t>
@@ -1583,10 +1580,18 @@
       </c>
     </row>
     <row r="90">
-      <c r="C90" s="5" t="n"/>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>BOE5.4</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="C91" s="5" t="n"/>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>CSOT6.75</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1600,56 +1605,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="10.5" customWidth="1" style="10" min="8" max="8"/>
+    <col width="10.5" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>IC</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Glass</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="n">
+      <c r="A2" s="10" t="n">
         <v>7272</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1689,7 +1694,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>7202H</t>
         </is>
@@ -1731,7 +1736,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>7202M</t>
         </is>
@@ -1773,7 +1778,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="10" t="n">
         <v>7302</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1851,7 +1856,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>7202MA</t>
         </is>
@@ -1883,6 +1888,9 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7371</v>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>海盛捷</t>
@@ -2348,6 +2356,20 @@
       <c r="B64" s="5" t="inlineStr">
         <is>
           <t>兴邦达</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>华谌智能</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>恒睿明</t>
         </is>
       </c>
     </row>
@@ -2366,1934 +2388,1934 @@
   <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="11.125" customWidth="1" style="10" min="2" max="2"/>
-    <col width="13.625" customWidth="1" style="10" min="4" max="4"/>
+    <col width="11.125" customWidth="1" style="8" min="2" max="2"/>
+    <col width="13.625" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>IC_Type</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Factory</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Glass</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>TP_Mode</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Palm</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="7" t="n">
         <v>7272</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>海菲</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>BOE4.95</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>调试中</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>郭泽昊</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>宋来</t>
         </is>
       </c>
-      <c r="K2" s="18" t="inlineStr">
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>2024年度</t>
         </is>
       </c>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="9" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="7" t="n">
         <v>7302</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>信利</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>BOE5.4</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>0flash</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>已调完</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>一类</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>王灵军</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>夏继进</t>
         </is>
       </c>
-      <c r="K3" s="18" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>2025年度</t>
         </is>
       </c>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="9" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="7" t="n">
         <v>7371</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>易快来</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>BOE5.45</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>1flash</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>关</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>已调试</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>二类</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>何世鹏</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>秦利敏</t>
         </is>
       </c>
-      <c r="K4" s="18" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>2026年度</t>
         </is>
       </c>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="9" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>7202M</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>联创</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>BOE5.46</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>待调试</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>三类</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>刘兰松</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>宋博玉</t>
         </is>
       </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>7202MA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>创维</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>BOE5.99</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>暂停</t>
         </is>
       </c>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>王辉</t>
         </is>
       </c>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>7272CA</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>同兴达</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>BOE6.088</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>关闭</t>
         </is>
       </c>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>肖潇</t>
         </is>
       </c>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>7302N</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>海盛捷</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>BOE6.517</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>量产</t>
         </is>
       </c>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>陈向波</t>
         </is>
       </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>壹星</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>BOE6.528</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>精卓</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>BOE6.56</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>三龙</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>BOE6.7</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>合力泰</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>BOE6.745</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>华显</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>BOE6.79</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>维立</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>BOE5.59</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>亿华</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>BOE6.95</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>立德</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>BOE6.96</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>晶泰</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>BOE6.82</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>德智欣</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>BOE6.88</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>中光电</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>CTO6.517</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>沛宏</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>CMI6.517</t>
         </is>
       </c>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="9" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>欣欣光电</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>CSOT6.67</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>众铭安</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>CSOT6.56</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>天正达</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>CSOT6.745</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>瑞恒</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>CSOT6.75</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="9" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>清创高</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>CSOT6.76</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>汉龙</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>CSOT6.78</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="9" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>晶胜通</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>CSOT6.88</t>
         </is>
       </c>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="9" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>龙煜</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>CTC5.45</t>
         </is>
       </c>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="9" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>金宏光电</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>CTC5.517</t>
         </is>
       </c>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="9" t="n"/>
-      <c r="M29" s="9" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>威达光电</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>CTC6.56</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="9" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>惠科</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>CTC6.67</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="9" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>华视</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>CTC6.88</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
-      <c r="L32" s="9" t="n"/>
-      <c r="M32" s="9" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>正金晶光电</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>CTC6.528</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
-      <c r="L33" s="9" t="n"/>
-      <c r="M33" s="9" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>华映</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>CTC6.95</t>
         </is>
       </c>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="9" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>长信新显</t>
         </is>
       </c>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>HK6.56</t>
         </is>
       </c>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="9" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>宏利</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>HKC6.517</t>
         </is>
       </c>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="9" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>泰启</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>HKC6.56</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="9" t="n"/>
-      <c r="M37" s="9" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>百业</t>
         </is>
       </c>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>HKC6.67</t>
         </is>
       </c>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="9" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>共赢</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>HKC6.745</t>
         </is>
       </c>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="9" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>德实</t>
         </is>
       </c>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>HKC6.88</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="9" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="7" t="n"/>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>京龙</t>
         </is>
       </c>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>HSD6.517</t>
         </is>
       </c>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="9" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>如新电子</t>
         </is>
       </c>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>HSD6.56</t>
         </is>
       </c>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="9" t="n"/>
-      <c r="M42" s="9" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>菲触显视</t>
         </is>
       </c>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>INX5.99</t>
         </is>
       </c>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
-      <c r="L43" s="9" t="n"/>
-      <c r="M43" s="9" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="7" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>轩达</t>
         </is>
       </c>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>INX6.517</t>
         </is>
       </c>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
-      <c r="L44" s="9" t="n"/>
-      <c r="M44" s="9" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>钜沣</t>
         </is>
       </c>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>INX6.56</t>
         </is>
       </c>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
-      <c r="L45" s="9" t="n"/>
-      <c r="M45" s="9" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>皓显</t>
         </is>
       </c>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>INX6.67</t>
         </is>
       </c>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
-      <c r="L46" s="9" t="n"/>
-      <c r="M46" s="9" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n"/>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>大通显示</t>
         </is>
       </c>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>INX6.78</t>
         </is>
       </c>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="9" t="n"/>
-      <c r="M47" s="9" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n"/>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>高展</t>
         </is>
       </c>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>INX6.82</t>
         </is>
       </c>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="9" t="n"/>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="9" t="n"/>
-      <c r="K48" s="9" t="n"/>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="9" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n"/>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>康华显通</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>INX6.95</t>
         </is>
       </c>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="9" t="n"/>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
-      <c r="L49" s="9" t="n"/>
-      <c r="M49" s="9" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>煜鑫</t>
         </is>
       </c>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>IVO6.28</t>
         </is>
       </c>
-      <c r="E50" s="9" t="n"/>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>宏利超显</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>IVO6.56</t>
         </is>
       </c>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
-      <c r="K51" s="9" t="n"/>
-      <c r="L51" s="9" t="n"/>
-      <c r="M51" s="9" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n"/>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>鹰芒技术</t>
         </is>
       </c>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>IVO6.088</t>
         </is>
       </c>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="9" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="7" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
+      <c r="M52" s="7" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="n"/>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>亿普拉斯</t>
         </is>
       </c>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>IVO6.75</t>
         </is>
       </c>
-      <c r="E53" s="9" t="n"/>
-      <c r="F53" s="9" t="n"/>
-      <c r="G53" s="9" t="n"/>
-      <c r="H53" s="9" t="n"/>
-      <c r="I53" s="9" t="n"/>
-      <c r="J53" s="9" t="n"/>
-      <c r="K53" s="9" t="n"/>
-      <c r="L53" s="9" t="n"/>
-      <c r="M53" s="9" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="7" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n"/>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>天山电子</t>
         </is>
       </c>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>IVO6.78</t>
         </is>
       </c>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-      <c r="I54" s="9" t="n"/>
-      <c r="J54" s="9" t="n"/>
-      <c r="K54" s="9" t="n"/>
-      <c r="L54" s="9" t="n"/>
-      <c r="M54" s="9" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+      <c r="J54" s="7" t="n"/>
+      <c r="K54" s="7" t="n"/>
+      <c r="L54" s="7" t="n"/>
+      <c r="M54" s="7" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n"/>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>凯晟</t>
         </is>
       </c>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>IVO6.79</t>
         </is>
       </c>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-      <c r="I55" s="9" t="n"/>
-      <c r="J55" s="9" t="n"/>
-      <c r="K55" s="9" t="n"/>
-      <c r="L55" s="9" t="n"/>
-      <c r="M55" s="9" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+      <c r="J55" s="7" t="n"/>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n"/>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>中正威</t>
         </is>
       </c>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>IVO6.517</t>
         </is>
       </c>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
-      <c r="L56" s="9" t="n"/>
-      <c r="M56" s="9" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+      <c r="J56" s="7" t="n"/>
+      <c r="K56" s="7" t="n"/>
+      <c r="L56" s="7" t="n"/>
+      <c r="M56" s="7" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="n"/>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>日日佳</t>
         </is>
       </c>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>MDT4.96</t>
         </is>
       </c>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="9" t="n"/>
-      <c r="H57" s="9" t="n"/>
-      <c r="I57" s="9" t="n"/>
-      <c r="J57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
-      <c r="L57" s="9" t="n"/>
-      <c r="M57" s="9" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+      <c r="J57" s="7" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>德普特</t>
         </is>
       </c>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>MDT5.45</t>
         </is>
       </c>
-      <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
-      <c r="H58" s="9" t="n"/>
-      <c r="I58" s="9" t="n"/>
-      <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
-      <c r="L58" s="9" t="n"/>
-      <c r="M58" s="9" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n"/>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>元格</t>
         </is>
       </c>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>MDT5.99</t>
         </is>
       </c>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="9" t="n"/>
-      <c r="J59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
-      <c r="L59" s="9" t="n"/>
-      <c r="M59" s="9" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+      <c r="J59" s="7" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="n"/>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>宏凯</t>
         </is>
       </c>
-      <c r="C60" s="9" t="n"/>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>MDT6.088</t>
         </is>
       </c>
-      <c r="E60" s="9" t="n"/>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="9" t="n"/>
-      <c r="I60" s="9" t="n"/>
-      <c r="J60" s="9" t="n"/>
-      <c r="K60" s="9" t="n"/>
-      <c r="L60" s="9" t="n"/>
-      <c r="M60" s="9" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>华佳</t>
         </is>
       </c>
-      <c r="C61" s="9" t="n"/>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>MDT6.517</t>
         </is>
       </c>
-      <c r="E61" s="9" t="n"/>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-      <c r="H61" s="9" t="n"/>
-      <c r="I61" s="9" t="n"/>
-      <c r="J61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-      <c r="L61" s="9" t="n"/>
-      <c r="M61" s="9" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+      <c r="J61" s="7" t="n"/>
+      <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="18" t="inlineStr">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>美力凯</t>
         </is>
       </c>
-      <c r="C62" s="9" t="n"/>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>MDT6.745</t>
         </is>
       </c>
-      <c r="E62" s="9" t="n"/>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
-      <c r="H62" s="9" t="n"/>
-      <c r="I62" s="9" t="n"/>
-      <c r="J62" s="9" t="n"/>
-      <c r="K62" s="9" t="n"/>
-      <c r="L62" s="9" t="n"/>
-      <c r="M62" s="9" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="n"/>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>联信康</t>
         </is>
       </c>
-      <c r="C63" s="9" t="n"/>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>MDT6.82</t>
         </is>
       </c>
-      <c r="E63" s="9" t="n"/>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="9" t="n"/>
-      <c r="H63" s="9" t="n"/>
-      <c r="I63" s="9" t="n"/>
-      <c r="J63" s="9" t="n"/>
-      <c r="K63" s="9" t="n"/>
-      <c r="L63" s="9" t="n"/>
-      <c r="M63" s="9" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
+      <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n"/>
-      <c r="B64" s="18" t="inlineStr">
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>兴邦达</t>
         </is>
       </c>
-      <c r="C64" s="9" t="n"/>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>SHARP6.517</t>
         </is>
       </c>
-      <c r="E64" s="9" t="n"/>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
-      <c r="H64" s="9" t="n"/>
-      <c r="I64" s="9" t="n"/>
-      <c r="J64" s="9" t="n"/>
-      <c r="K64" s="9" t="n"/>
-      <c r="L64" s="9" t="n"/>
-      <c r="M64" s="9" t="n"/>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="7" t="n"/>
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n"/>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>华夏彩沛宏</t>
         </is>
       </c>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>SHARP6.72</t>
         </is>
       </c>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
-      <c r="L65" s="9" t="n"/>
-      <c r="M65" s="9" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+      <c r="J65" s="7" t="n"/>
+      <c r="K65" s="7" t="n"/>
+      <c r="L65" s="7" t="n"/>
+      <c r="M65" s="7" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n"/>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>睿智威</t>
         </is>
       </c>
-      <c r="C66" s="9" t="n"/>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="14" t="inlineStr">
         <is>
           <t>SHARP6.745</t>
         </is>
       </c>
-      <c r="E66" s="9" t="n"/>
-      <c r="F66" s="9" t="n"/>
-      <c r="G66" s="9" t="n"/>
-      <c r="H66" s="9" t="n"/>
-      <c r="I66" s="9" t="n"/>
-      <c r="J66" s="9" t="n"/>
-      <c r="K66" s="9" t="n"/>
-      <c r="L66" s="9" t="n"/>
-      <c r="M66" s="9" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="n"/>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>TM4.96</t>
         </is>
       </c>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="9" t="n"/>
-      <c r="G67" s="9" t="n"/>
-      <c r="H67" s="9" t="n"/>
-      <c r="I67" s="9" t="n"/>
-      <c r="J67" s="9" t="n"/>
-      <c r="K67" s="9" t="n"/>
-      <c r="L67" s="9" t="n"/>
-      <c r="M67" s="9" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
+      <c r="G67" s="7" t="n"/>
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+      <c r="J67" s="7" t="n"/>
+      <c r="K67" s="7" t="n"/>
+      <c r="L67" s="7" t="n"/>
+      <c r="M67" s="7" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n"/>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="9" t="n"/>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="14" t="inlineStr">
         <is>
           <t>TM6.67</t>
         </is>
       </c>
-      <c r="E68" s="9" t="n"/>
-      <c r="F68" s="9" t="n"/>
-      <c r="G68" s="9" t="n"/>
-      <c r="H68" s="9" t="n"/>
-      <c r="I68" s="9" t="n"/>
-      <c r="J68" s="9" t="n"/>
-      <c r="K68" s="9" t="n"/>
-      <c r="L68" s="9" t="n"/>
-      <c r="M68" s="9" t="n"/>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+      <c r="J68" s="7" t="n"/>
+      <c r="K68" s="7" t="n"/>
+      <c r="L68" s="7" t="n"/>
+      <c r="M68" s="7" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="n"/>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>TM6.78</t>
         </is>
       </c>
-      <c r="E69" s="9" t="n"/>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
-      <c r="L69" s="9" t="n"/>
-      <c r="M69" s="9" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+      <c r="J69" s="7" t="n"/>
+      <c r="K69" s="7" t="n"/>
+      <c r="L69" s="7" t="n"/>
+      <c r="M69" s="7" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n"/>
-      <c r="B70" s="9" t="n"/>
-      <c r="C70" s="9" t="n"/>
-      <c r="D70" s="18" t="inlineStr">
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>TRULY6.46</t>
         </is>
       </c>
-      <c r="E70" s="9" t="n"/>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="9" t="n"/>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="9" t="n"/>
-      <c r="K70" s="9" t="n"/>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="9" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="7" t="n"/>
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+      <c r="J70" s="7" t="n"/>
+      <c r="K70" s="7" t="n"/>
+      <c r="L70" s="7" t="n"/>
+      <c r="M70" s="7" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="n"/>
-      <c r="B71" s="9" t="n"/>
-      <c r="C71" s="9" t="n"/>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>TRULY6.3</t>
         </is>
       </c>
-      <c r="E71" s="9" t="n"/>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
-      <c r="H71" s="9" t="n"/>
-      <c r="I71" s="9" t="n"/>
-      <c r="J71" s="9" t="n"/>
-      <c r="K71" s="9" t="n"/>
-      <c r="L71" s="9" t="n"/>
-      <c r="M71" s="9" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+      <c r="J71" s="7" t="n"/>
+      <c r="K71" s="7" t="n"/>
+      <c r="L71" s="7" t="n"/>
+      <c r="M71" s="7" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n"/>
-      <c r="B72" s="9" t="n"/>
-      <c r="C72" s="9" t="n"/>
-      <c r="D72" s="18" t="inlineStr">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>TRULY6.517</t>
         </is>
       </c>
-      <c r="E72" s="9" t="n"/>
-      <c r="F72" s="9" t="n"/>
-      <c r="G72" s="9" t="n"/>
-      <c r="H72" s="9" t="n"/>
-      <c r="I72" s="9" t="n"/>
-      <c r="J72" s="9" t="n"/>
-      <c r="K72" s="9" t="n"/>
-      <c r="L72" s="9" t="n"/>
-      <c r="M72" s="9" t="n"/>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+      <c r="J72" s="7" t="n"/>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="7" t="n"/>
+      <c r="M72" s="7" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="n"/>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="18" t="inlineStr">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>TRULY6.745</t>
         </is>
       </c>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
-      <c r="L73" s="9" t="n"/>
-      <c r="M73" s="9" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="7" t="n"/>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n"/>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="A74" s="7" t="n"/>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="14" t="inlineStr">
         <is>
           <t>PANDA6.517</t>
         </is>
       </c>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
-      <c r="H74" s="9" t="n"/>
-      <c r="I74" s="9" t="n"/>
-      <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
-      <c r="L74" s="9" t="n"/>
-      <c r="M74" s="9" t="n"/>
+      <c r="E74" s="7" t="n"/>
+      <c r="F74" s="7" t="n"/>
+      <c r="G74" s="7" t="n"/>
+      <c r="H74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
+      <c r="J74" s="7" t="n"/>
+      <c r="K74" s="7" t="n"/>
+      <c r="L74" s="7" t="n"/>
+      <c r="M74" s="7" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="n"/>
-      <c r="B75" s="9" t="n"/>
-      <c r="C75" s="9" t="n"/>
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
       <c r="D75" s="5" t="n"/>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="9" t="n"/>
-      <c r="K75" s="9" t="n"/>
-      <c r="L75" s="9" t="n"/>
-      <c r="M75" s="9" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
+      <c r="J75" s="7" t="n"/>
+      <c r="K75" s="7" t="n"/>
+      <c r="L75" s="7" t="n"/>
+      <c r="M75" s="7" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="n"/>
-      <c r="B76" s="9" t="n"/>
-      <c r="C76" s="9" t="n"/>
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
       <c r="D76" s="5" t="n"/>
-      <c r="E76" s="9" t="n"/>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
-      <c r="H76" s="9" t="n"/>
-      <c r="I76" s="9" t="n"/>
-      <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
-      <c r="L76" s="9" t="n"/>
-      <c r="M76" s="9" t="n"/>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="n"/>
+      <c r="I76" s="7" t="n"/>
+      <c r="J76" s="7" t="n"/>
+      <c r="K76" s="7" t="n"/>
+      <c r="L76" s="7" t="n"/>
+      <c r="M76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="D77" s="5" t="n"/>

--- a/compare_information.xlsx
+++ b/compare_information.xlsx
@@ -67,7 +67,6 @@
     <font>
       <name val="等线"/>
       <charset val="134"/>
-      <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
@@ -128,9 +127,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -144,9 +140,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -162,6 +155,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,19 +500,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col width="14" customWidth="1" style="8" min="1" max="1"/>
-    <col width="24.625" customWidth="1" style="8" min="2" max="2"/>
-    <col width="33.375" customWidth="1" style="8" min="3" max="3"/>
-    <col width="21.5" customWidth="1" style="8" min="4" max="4"/>
-    <col width="23.625" customWidth="1" style="8" min="5" max="5"/>
-    <col width="27.25" customWidth="1" style="8" min="6" max="6"/>
-    <col width="18.625" customWidth="1" style="8" min="9" max="9"/>
+    <col width="14" customWidth="1" style="7" min="1" max="1"/>
+    <col width="24.625" customWidth="1" style="7" min="2" max="2"/>
+    <col width="33.375" customWidth="1" style="7" min="3" max="3"/>
+    <col width="21.5" customWidth="1" style="7" min="4" max="4"/>
+    <col width="23.625" customWidth="1" style="7" min="5" max="5"/>
+    <col width="27.25" customWidth="1" style="7" min="6" max="6"/>
+    <col width="18.625" customWidth="1" style="7" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="8">
+    <row r="1" ht="15.6" customHeight="1" s="7">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>IC</t>
@@ -530,7 +529,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.9" customHeight="1" s="8">
+    <row r="2" ht="13.9" customHeight="1" s="7">
       <c r="A2" s="2" t="n">
         <v>7272</v>
       </c>
@@ -539,14 +538,14 @@
           <t>V1.0.0.8_20220309</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>CSOT6.78</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.9" customHeight="1" s="8">
-      <c r="A3" s="14" t="inlineStr">
+    <row r="3" ht="13.9" customHeight="1" s="7">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>7202M</t>
         </is>
@@ -556,7 +555,7 @@
           <t>V1.0.0.8_20220321</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>TM6.58</t>
         </is>
@@ -573,14 +572,14 @@
           <t>V1.0.0.9_20220511</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>IVO6.517</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>7202H 7202M</t>
         </is>
@@ -590,14 +589,14 @@
           <t>V1.0.0.11_20220805</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>TRULY6.517</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>7202M 7202H</t>
         </is>
@@ -607,14 +606,14 @@
           <t>V1.0.0.11_20220824</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>BOE6.088</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>7302B</t>
         </is>
@@ -624,13 +623,13 @@
           <t>V1.0.1.4_20221121</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>CTO6.517</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="15" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -641,16 +640,16 @@
           <t>V1.0.1.5_20230105</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>PANDA6.517</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>7272CA</t>
         </is>
@@ -660,16 +659,16 @@
           <t>V1.0.1.5_20230213</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>SHARP6.517</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="14" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>7202MA</t>
         </is>
@@ -679,13 +678,13 @@
           <t>V1.0.1.5_20230220</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>MDT6.517</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -696,42 +695,50 @@
           <t>V1.0.1.5_20230228</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>CTC6.517</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7274RA</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>V1.0.1.5_20230317</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>INX6.517</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>7205C</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>V1.0.1.6_20230410</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>HKC6.517</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n"/>
+      <c r="F13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -740,13 +747,13 @@
           <t>V1.0.1.7_20230417</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>HKC6.517 1-1</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="7" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -755,12 +762,12 @@
           <t>V1.0.1.7_20230418</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>HKC6.517 3-1</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n"/>
+      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -769,7 +776,7 @@
           <t>V1.0.1.7_20230427</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>HKC6.517 4-1</t>
         </is>
@@ -782,7 +789,7 @@
           <t>V1.0.1.8_20230506</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>HKC6.517 5-1</t>
         </is>
@@ -795,7 +802,7 @@
           <t>V1.0.1.8_20230530</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>HKC6.517 7-1</t>
         </is>
@@ -808,7 +815,7 @@
           <t>V1.0.1.8_20230601</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>BOE5.45</t>
         </is>
@@ -821,7 +828,7 @@
           <t>V1.0.1.8_20230606</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>BOE6.59</t>
         </is>
@@ -829,12 +836,12 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>V1.0.1.8_20230526</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>HSD6.517</t>
         </is>
@@ -847,7 +854,7 @@
           <t>V1.0.1.10_20230616</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>INX5.99</t>
         </is>
@@ -861,7 +868,7 @@
           <t>V1.0.1.10_20230619</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>BOE6.517</t>
         </is>
@@ -874,7 +881,7 @@
           <t>V1.0.1.10_20230629</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MDT5.45 </t>
         </is>
@@ -882,12 +889,12 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>V1.0.1.13_20230719</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>IVO6.55</t>
         </is>
@@ -900,7 +907,7 @@
           <t>V1.0.1.13_20230712</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>CTC6.528</t>
         </is>
@@ -913,7 +920,7 @@
           <t>V1.0.1.14_20230725</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>MDT6.745</t>
         </is>
@@ -926,7 +933,7 @@
           <t>V1.0.1.14_20230726</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>IVO6.088</t>
         </is>
@@ -939,7 +946,7 @@
           <t>V1.0.1.14_20230727</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>HKC6.56</t>
         </is>
@@ -952,7 +959,7 @@
           <t>V1.0.1.14_20230803</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>BOE6.95</t>
         </is>
@@ -965,7 +972,7 @@
           <t>V1.0.1.14_20231025</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>HKC6.745</t>
         </is>
@@ -973,12 +980,12 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>V1.0.1.16_20230825</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>SHARP6.745</t>
         </is>
@@ -991,7 +998,7 @@
           <t>V1.0.1.17_20230911</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>INX6.56</t>
         </is>
@@ -1004,7 +1011,7 @@
           <t>V1.0.1.17_20230914</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>INX6.56</t>
         </is>
@@ -1017,7 +1024,7 @@
           <t>V1.0.1.17_20230921</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>INX6.82</t>
         </is>
@@ -1030,7 +1037,7 @@
           <t>V1.0.1.17_20230921_8</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>TRULY6.745</t>
         </is>
@@ -1043,7 +1050,7 @@
           <t>V1.0.1.19_20231016</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>BOE6.82</t>
         </is>
@@ -1056,7 +1063,7 @@
           <t>V1.0.1.19_20231020_1</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>TRULY6.3</t>
         </is>
@@ -1069,7 +1076,7 @@
           <t>V1.0.1.20_20230827_1</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>MDT6.088</t>
         </is>
@@ -1082,7 +1089,7 @@
           <t>V1.0.1.20_20231025</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>INX6.95</t>
         </is>
@@ -1095,7 +1102,7 @@
           <t>V1.0.1.20_20231026</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>HKC6.217</t>
         </is>
@@ -1108,7 +1115,7 @@
           <t>V1.0.1.20_20231103</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>SHARP6.72</t>
         </is>
@@ -1121,7 +1128,7 @@
           <t>V1.0.1.21_20231107</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>CTC6.56</t>
         </is>
@@ -1134,7 +1141,7 @@
           <t>V1.0.1.22_20231212</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>BOE6.79</t>
         </is>
@@ -1147,7 +1154,7 @@
           <t>V1.0.1.23_20231226</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">BOE5.99    </t>
         </is>
@@ -1160,7 +1167,7 @@
           <t>V1.0.1.24_20240119</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>HSD6.745</t>
         </is>
@@ -1173,7 +1180,7 @@
           <t>V1.0.1.25_20240531</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">IVO6.28  </t>
         </is>
@@ -1186,7 +1193,7 @@
           <t>V1.0.1.25_20240628</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>CTC6.67</t>
         </is>
@@ -1199,7 +1206,7 @@
           <t>V1.0.1.26_20240726</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>CTC6.56</t>
         </is>
@@ -1212,7 +1219,7 @@
           <t>V1.0.1.26_20240802_2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>TRULY6.46</t>
         </is>
@@ -1225,7 +1232,7 @@
           <t>V1.0.1.27_20240822</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>MDT4.96</t>
         </is>
@@ -1238,7 +1245,7 @@
           <t>V1.0.1.28_20241018</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>HSD6.56</t>
         </is>
@@ -1251,7 +1258,7 @@
           <t>V1.0.1.28_20241104</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>CSOT6.745</t>
         </is>
@@ -1264,7 +1271,7 @@
           <t>V1.0.1.29_20241105</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>INX6.67</t>
         </is>
@@ -1277,7 +1284,7 @@
           <t>V1.0.1.30_20241211</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>BOE6.745</t>
         </is>
@@ -1290,7 +1297,7 @@
           <t>V1.0.1.31_20250429</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>INX6.56_A28</t>
         </is>
@@ -1303,7 +1310,7 @@
           <t>V1.0.1.31_20250402</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>CTC6.88</t>
         </is>
@@ -1316,7 +1323,7 @@
           <t>V1.0.1.32_20251110</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>CSOT6.56</t>
         </is>
@@ -1324,12 +1331,12 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>V1.0.1.33_20251127</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>IVO6.56</t>
         </is>
@@ -1337,12 +1344,12 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>V1.0.1.34_20260311</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>HKC6.67</t>
         </is>
@@ -1350,8 +1357,12 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>V1.0.1.35_20260414</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>IVO6.79</t>
         </is>
@@ -1359,8 +1370,12 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>V1.0.1.35_20260428</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>HKC6.56 4-1</t>
         </is>
@@ -1368,8 +1383,12 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>V1.0.1.35_20260527</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>BOE5.7</t>
         </is>
@@ -1377,8 +1396,8 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="B64" s="15" t="n"/>
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>IVO6.75</t>
         </is>
@@ -1386,8 +1405,8 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="B65" s="15" t="n"/>
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>HKC6.88</t>
         </is>
@@ -1395,8 +1414,8 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>CSOT6.67</t>
         </is>
@@ -1405,7 +1424,7 @@
     <row r="67">
       <c r="A67" s="2" t="n"/>
       <c r="B67" s="2" t="n"/>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>BOE6.56</t>
         </is>
@@ -1414,7 +1433,7 @@
     <row r="68">
       <c r="A68" s="2" t="n"/>
       <c r="B68" s="2" t="n"/>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>HKC6.56 1-1</t>
         </is>
@@ -1423,7 +1442,7 @@
     <row r="69">
       <c r="A69" s="2" t="n"/>
       <c r="B69" s="2" t="n"/>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>HKC6.56 3-1</t>
         </is>
@@ -1432,7 +1451,7 @@
     <row r="70">
       <c r="A70" s="2" t="n"/>
       <c r="B70" s="2" t="n"/>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>MDT6.517B版</t>
         </is>
@@ -1441,7 +1460,7 @@
     <row r="71">
       <c r="A71" s="2" t="n"/>
       <c r="B71" s="2" t="n"/>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>CSOT6.88</t>
         </is>
@@ -1450,7 +1469,7 @@
     <row r="72">
       <c r="A72" s="2" t="n"/>
       <c r="B72" s="2" t="n"/>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>IVO6.78</t>
         </is>
@@ -1459,7 +1478,7 @@
     <row r="73">
       <c r="A73" s="2" t="n"/>
       <c r="B73" s="2" t="n"/>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>BOE6.528</t>
         </is>
@@ -1467,7 +1486,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>INX6.78</t>
         </is>
@@ -1503,7 +1522,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>CTC5.45</t>
         </is>
@@ -1524,42 +1543,42 @@
       </c>
     </row>
     <row r="82">
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>CSOT6.88</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>HKC6.56</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>CTC6.95</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>TM4.96</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>BOE6.88</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>MDT6.088</t>
         </is>
@@ -1573,23 +1592,37 @@
       </c>
     </row>
     <row r="89">
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>BOE6.088</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>BOE5.4</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>CSOT6.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TM6.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BOE6.78</t>
         </is>
       </c>
     </row>
@@ -1605,56 +1638,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="10.5" customWidth="1" style="8" min="8" max="8"/>
+    <col width="10.5" customWidth="1" style="7" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>IC</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Glass</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="14" t="n">
         <v>7272</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1687,14 +1720,14 @@
           <t>黄耀</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>TDDIRobot</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>7202H</t>
         </is>
@@ -1729,14 +1762,14 @@
           <t>吴宏博</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>kakarot</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>7202M</t>
         </is>
@@ -1771,14 +1804,14 @@
           <t>丁淑芳</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>nico</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="14" t="n">
         <v>7302</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1811,14 +1844,14 @@
           <t>成鹏</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>shine</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>7272CA</t>
         </is>
@@ -1838,7 +1871,7 @@
           <t>2026年度</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>模组工艺</t>
@@ -1849,14 +1882,14 @@
           <t>李尚聪</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>shangcong</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>7202MA</t>
         </is>
@@ -1881,14 +1914,14 @@
           <t>卓秀慧</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>xiuhui</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="15" t="n">
         <v>7371</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1906,13 +1939,18 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>evan</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>7205C</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>壹星</t>
@@ -1928,13 +1966,18 @@
           <t>误判</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>peng</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>7274RA</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>精卓</t>
@@ -1945,7 +1988,7 @@
           <t>HKC</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>整机软件</t>
         </is>
@@ -1962,7 +2005,7 @@
           <t>HSD</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>模组物料</t>
         </is>
@@ -1979,7 +2022,7 @@
           <t>INX</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>整机干扰</t>
         </is>
@@ -2339,21 +2382,21 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>美力凯</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>联信康</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>兴邦达</t>
         </is>
@@ -2370,6 +2413,34 @@
       <c r="B66" t="inlineStr">
         <is>
           <t>恒睿明</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>时钰</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>华捷胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>固显</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>德莱</t>
         </is>
       </c>
     </row>
@@ -2388,2015 +2459,2015 @@
   <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="11.125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="13.625" customWidth="1" style="8" min="4" max="4"/>
+    <col width="11.125" customWidth="1" style="7" min="2" max="2"/>
+    <col width="13.625" customWidth="1" style="7" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>IC_Type</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Factory</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Glass</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>TP_Mode</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Palm</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="6" t="n">
         <v>7272</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>海菲</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>BOE4.95</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>调试中</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>郭泽昊</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>宋来</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>2024年度</t>
         </is>
       </c>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="6" t="n">
         <v>7302</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>信利</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>BOE5.4</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>0flash</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>已调完</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>一类</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>王灵军</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>夏继进</t>
         </is>
       </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>2025年度</t>
         </is>
       </c>
-      <c r="L3" s="7" t="n"/>
-      <c r="M3" s="7" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="6" t="n">
         <v>7371</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>易快来</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>BOE5.45</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>1flash</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>关</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>已调试</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>二类</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>何世鹏</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>秦利敏</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>2026年度</t>
         </is>
       </c>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="7" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>7202M</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>联创</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>BOE5.46</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>待调试</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>三类</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>刘兰松</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>宋博玉</t>
         </is>
       </c>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>7202MA</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>创维</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>BOE5.99</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>暂停</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>王辉</t>
         </is>
       </c>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>7272CA</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>同兴达</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>BOE6.088</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>关闭</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>肖潇</t>
         </is>
       </c>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>7302N</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>海盛捷</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>BOE6.517</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>量产</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>陈向波</t>
         </is>
       </c>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>壹星</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>BOE6.528</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>精卓</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>BOE6.56</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>三龙</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>BOE6.7</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>合力泰</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>BOE6.745</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>华显</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>BOE6.79</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>维立</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>BOE5.59</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>亿华</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>BOE6.95</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>立德</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>BOE6.96</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>晶泰</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>BOE6.82</t>
         </is>
       </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>德智欣</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>BOE6.88</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>中光电</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>CTO6.517</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>沛宏</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>CMI6.517</t>
         </is>
       </c>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>欣欣光电</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>CSOT6.67</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>众铭安</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>CSOT6.56</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>天正达</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>CSOT6.745</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>瑞恒</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>CSOT6.75</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>清创高</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>CSOT6.76</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>汉龙</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>CSOT6.78</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>晶胜通</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>CSOT6.88</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>龙煜</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>CTC5.45</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>金宏光电</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>CTC5.517</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>威达光电</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>CTC6.56</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>惠科</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>CTC6.67</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>华视</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>CTC6.88</t>
         </is>
       </c>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
-      <c r="K32" s="7" t="n"/>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>正金晶光电</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>CTC6.528</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n"/>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>华映</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>CTC6.95</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>长信新显</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>HK6.56</t>
         </is>
       </c>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>宏利</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>HKC6.517</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>泰启</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>HKC6.56</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>百业</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>HKC6.67</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>共赢</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>HKC6.745</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="7" t="n"/>
-      <c r="J39" s="7" t="n"/>
-      <c r="K39" s="7" t="n"/>
-      <c r="L39" s="7" t="n"/>
-      <c r="M39" s="7" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n"/>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>德实</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>HKC6.88</t>
         </is>
       </c>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="7" t="n"/>
-      <c r="L40" s="7" t="n"/>
-      <c r="M40" s="7" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>京龙</t>
         </is>
       </c>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>HSD6.517</t>
         </is>
       </c>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
-      <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>如新电子</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>HSD6.56</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="7" t="n"/>
-      <c r="J42" s="7" t="n"/>
-      <c r="K42" s="7" t="n"/>
-      <c r="L42" s="7" t="n"/>
-      <c r="M42" s="7" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n"/>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>菲触显视</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>INX5.99</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n"/>
-      <c r="J43" s="7" t="n"/>
-      <c r="K43" s="7" t="n"/>
-      <c r="L43" s="7" t="n"/>
-      <c r="M43" s="7" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n"/>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>轩达</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>INX6.517</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
-      <c r="J44" s="7" t="n"/>
-      <c r="K44" s="7" t="n"/>
-      <c r="L44" s="7" t="n"/>
-      <c r="M44" s="7" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n"/>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>钜沣</t>
         </is>
       </c>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>INX6.56</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
-      <c r="J45" s="7" t="n"/>
-      <c r="K45" s="7" t="n"/>
-      <c r="L45" s="7" t="n"/>
-      <c r="M45" s="7" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="n"/>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>皓显</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>INX6.67</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="K46" s="7" t="n"/>
-      <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n"/>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>大通显示</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>INX6.78</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="7" t="n"/>
-      <c r="K47" s="7" t="n"/>
-      <c r="L47" s="7" t="n"/>
-      <c r="M47" s="7" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n"/>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>高展</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>INX6.82</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="7" t="n"/>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-      <c r="J48" s="7" t="n"/>
-      <c r="K48" s="7" t="n"/>
-      <c r="L48" s="7" t="n"/>
-      <c r="M48" s="7" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>康华显通</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>INX6.95</t>
         </is>
       </c>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n"/>
-      <c r="L49" s="7" t="n"/>
-      <c r="M49" s="7" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n"/>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>煜鑫</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>IVO6.28</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
-      <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="n"/>
-      <c r="I50" s="7" t="n"/>
-      <c r="J50" s="7" t="n"/>
-      <c r="K50" s="7" t="n"/>
-      <c r="L50" s="7" t="n"/>
-      <c r="M50" s="7" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n"/>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>宏利超显</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>IVO6.56</t>
         </is>
       </c>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n"/>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>鹰芒技术</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>IVO6.088</t>
         </is>
       </c>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
-      <c r="J52" s="7" t="n"/>
-      <c r="K52" s="7" t="n"/>
-      <c r="L52" s="7" t="n"/>
-      <c r="M52" s="7" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n"/>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>亿普拉斯</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>IVO6.75</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="7" t="n"/>
-      <c r="J53" s="7" t="n"/>
-      <c r="K53" s="7" t="n"/>
-      <c r="L53" s="7" t="n"/>
-      <c r="M53" s="7" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n"/>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>天山电子</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>IVO6.78</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
-      <c r="J54" s="7" t="n"/>
-      <c r="K54" s="7" t="n"/>
-      <c r="L54" s="7" t="n"/>
-      <c r="M54" s="7" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
+      <c r="I54" s="6" t="n"/>
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="n"/>
+      <c r="M54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n"/>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>凯晟</t>
         </is>
       </c>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>IVO6.79</t>
         </is>
       </c>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
-      <c r="J55" s="7" t="n"/>
-      <c r="K55" s="7" t="n"/>
-      <c r="L55" s="7" t="n"/>
-      <c r="M55" s="7" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="n"/>
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="n"/>
+      <c r="M55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n"/>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>中正威</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>IVO6.517</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
-      <c r="J56" s="7" t="n"/>
-      <c r="K56" s="7" t="n"/>
-      <c r="L56" s="7" t="n"/>
-      <c r="M56" s="7" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
+      <c r="I56" s="6" t="n"/>
+      <c r="J56" s="6" t="n"/>
+      <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n"/>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>日日佳</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>MDT4.96</t>
         </is>
       </c>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="7" t="n"/>
-      <c r="J57" s="7" t="n"/>
-      <c r="K57" s="7" t="n"/>
-      <c r="L57" s="7" t="n"/>
-      <c r="M57" s="7" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="n"/>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="n"/>
+      <c r="M57" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n"/>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>德普特</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>MDT5.45</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="n"/>
-      <c r="I58" s="7" t="n"/>
-      <c r="J58" s="7" t="n"/>
-      <c r="K58" s="7" t="n"/>
-      <c r="L58" s="7" t="n"/>
-      <c r="M58" s="7" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="n"/>
+      <c r="J58" s="6" t="n"/>
+      <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="n"/>
+      <c r="M58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n"/>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>元格</t>
         </is>
       </c>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>MDT5.99</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
-      <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
-      <c r="J59" s="7" t="n"/>
-      <c r="K59" s="7" t="n"/>
-      <c r="L59" s="7" t="n"/>
-      <c r="M59" s="7" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="n"/>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="n"/>
+      <c r="M59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n"/>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>宏凯</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>MDT6.088</t>
         </is>
       </c>
-      <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
-      <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="7" t="n"/>
-      <c r="J60" s="7" t="n"/>
-      <c r="K60" s="7" t="n"/>
-      <c r="L60" s="7" t="n"/>
-      <c r="M60" s="7" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="6" t="n"/>
+      <c r="J60" s="6" t="n"/>
+      <c r="K60" s="6" t="n"/>
+      <c r="L60" s="6" t="n"/>
+      <c r="M60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n"/>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>华佳</t>
         </is>
       </c>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>MDT6.517</t>
         </is>
       </c>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
-      <c r="M61" s="7" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
+      <c r="I61" s="6" t="n"/>
+      <c r="J61" s="6" t="n"/>
+      <c r="K61" s="6" t="n"/>
+      <c r="L61" s="6" t="n"/>
+      <c r="M61" s="6" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>美力凯</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="14" t="inlineStr">
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>MDT6.745</t>
         </is>
       </c>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
-      <c r="K62" s="7" t="n"/>
-      <c r="L62" s="7" t="n"/>
-      <c r="M62" s="7" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="6" t="n"/>
+      <c r="J62" s="6" t="n"/>
+      <c r="K62" s="6" t="n"/>
+      <c r="L62" s="6" t="n"/>
+      <c r="M62" s="6" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n"/>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>联信康</t>
         </is>
       </c>
-      <c r="C63" s="7" t="n"/>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>MDT6.82</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
-      <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="7" t="n"/>
-      <c r="J63" s="7" t="n"/>
-      <c r="K63" s="7" t="n"/>
-      <c r="L63" s="7" t="n"/>
-      <c r="M63" s="7" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="6" t="n"/>
+      <c r="I63" s="6" t="n"/>
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="6" t="n"/>
+      <c r="L63" s="6" t="n"/>
+      <c r="M63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n"/>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>兴邦达</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>SHARP6.517</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-      <c r="J64" s="7" t="n"/>
-      <c r="K64" s="7" t="n"/>
-      <c r="L64" s="7" t="n"/>
-      <c r="M64" s="7" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="6" t="n"/>
+      <c r="I64" s="6" t="n"/>
+      <c r="J64" s="6" t="n"/>
+      <c r="K64" s="6" t="n"/>
+      <c r="L64" s="6" t="n"/>
+      <c r="M64" s="6" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="n"/>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>华夏彩沛宏</t>
         </is>
       </c>
-      <c r="C65" s="7" t="n"/>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>SHARP6.72</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
-      <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
-      <c r="I65" s="7" t="n"/>
-      <c r="J65" s="7" t="n"/>
-      <c r="K65" s="7" t="n"/>
-      <c r="L65" s="7" t="n"/>
-      <c r="M65" s="7" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="6" t="n"/>
+      <c r="J65" s="6" t="n"/>
+      <c r="K65" s="6" t="n"/>
+      <c r="L65" s="6" t="n"/>
+      <c r="M65" s="6" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="n"/>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>睿智威</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>SHARP6.745</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
-      <c r="K66" s="7" t="n"/>
-      <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="6" t="n"/>
+      <c r="I66" s="6" t="n"/>
+      <c r="J66" s="6" t="n"/>
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="6" t="n"/>
+      <c r="M66" s="6" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>TM4.96</t>
         </is>
       </c>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n"/>
-      <c r="J67" s="7" t="n"/>
-      <c r="K67" s="7" t="n"/>
-      <c r="L67" s="7" t="n"/>
-      <c r="M67" s="7" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="6" t="n"/>
+      <c r="I67" s="6" t="n"/>
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="6" t="n"/>
+      <c r="M67" s="6" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="n"/>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="7" t="n"/>
-      <c r="D68" s="14" t="inlineStr">
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>TM6.67</t>
         </is>
       </c>
-      <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="n"/>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
-      <c r="I68" s="7" t="n"/>
-      <c r="J68" s="7" t="n"/>
-      <c r="K68" s="7" t="n"/>
-      <c r="L68" s="7" t="n"/>
-      <c r="M68" s="7" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="6" t="n"/>
+      <c r="I68" s="6" t="n"/>
+      <c r="J68" s="6" t="n"/>
+      <c r="K68" s="6" t="n"/>
+      <c r="L68" s="6" t="n"/>
+      <c r="M68" s="6" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="14" t="inlineStr">
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>TM6.78</t>
         </is>
       </c>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
-      <c r="J69" s="7" t="n"/>
-      <c r="K69" s="7" t="n"/>
-      <c r="L69" s="7" t="n"/>
-      <c r="M69" s="7" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="6" t="n"/>
+      <c r="I69" s="6" t="n"/>
+      <c r="J69" s="6" t="n"/>
+      <c r="K69" s="6" t="n"/>
+      <c r="L69" s="6" t="n"/>
+      <c r="M69" s="6" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n"/>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>TRULY6.46</t>
         </is>
       </c>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
-      <c r="I70" s="7" t="n"/>
-      <c r="J70" s="7" t="n"/>
-      <c r="K70" s="7" t="n"/>
-      <c r="L70" s="7" t="n"/>
-      <c r="M70" s="7" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+      <c r="G70" s="6" t="n"/>
+      <c r="H70" s="6" t="n"/>
+      <c r="I70" s="6" t="n"/>
+      <c r="J70" s="6" t="n"/>
+      <c r="K70" s="6" t="n"/>
+      <c r="L70" s="6" t="n"/>
+      <c r="M70" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="n"/>
-      <c r="B71" s="7" t="n"/>
-      <c r="C71" s="7" t="n"/>
-      <c r="D71" s="15" t="inlineStr">
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>TRULY6.3</t>
         </is>
       </c>
-      <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="n"/>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
-      <c r="I71" s="7" t="n"/>
-      <c r="J71" s="7" t="n"/>
-      <c r="K71" s="7" t="n"/>
-      <c r="L71" s="7" t="n"/>
-      <c r="M71" s="7" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="6" t="n"/>
+      <c r="J71" s="6" t="n"/>
+      <c r="K71" s="6" t="n"/>
+      <c r="L71" s="6" t="n"/>
+      <c r="M71" s="6" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="n"/>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="7" t="n"/>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>TRULY6.517</t>
         </is>
       </c>
-      <c r="E72" s="7" t="n"/>
-      <c r="F72" s="7" t="n"/>
-      <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
-      <c r="J72" s="7" t="n"/>
-      <c r="K72" s="7" t="n"/>
-      <c r="L72" s="7" t="n"/>
-      <c r="M72" s="7" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="6" t="n"/>
+      <c r="I72" s="6" t="n"/>
+      <c r="J72" s="6" t="n"/>
+      <c r="K72" s="6" t="n"/>
+      <c r="L72" s="6" t="n"/>
+      <c r="M72" s="6" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="n"/>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="7" t="n"/>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>TRULY6.745</t>
         </is>
       </c>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
-      <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
-      <c r="I73" s="7" t="n"/>
-      <c r="J73" s="7" t="n"/>
-      <c r="K73" s="7" t="n"/>
-      <c r="L73" s="7" t="n"/>
-      <c r="M73" s="7" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="6" t="n"/>
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="6" t="n"/>
+      <c r="L73" s="6" t="n"/>
+      <c r="M73" s="6" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="n"/>
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="7" t="n"/>
-      <c r="D74" s="14" t="inlineStr">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>PANDA6.517</t>
         </is>
       </c>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
-      <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
-      <c r="J74" s="7" t="n"/>
-      <c r="K74" s="7" t="n"/>
-      <c r="L74" s="7" t="n"/>
-      <c r="M74" s="7" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="6" t="n"/>
+      <c r="I74" s="6" t="n"/>
+      <c r="J74" s="6" t="n"/>
+      <c r="K74" s="6" t="n"/>
+      <c r="L74" s="6" t="n"/>
+      <c r="M74" s="6" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="n"/>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="7" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="n"/>
-      <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
-      <c r="J75" s="7" t="n"/>
-      <c r="K75" s="7" t="n"/>
-      <c r="L75" s="7" t="n"/>
-      <c r="M75" s="7" t="n"/>
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="6" t="n"/>
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="n"/>
+      <c r="L75" s="6" t="n"/>
+      <c r="M75" s="6" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="n"/>
-      <c r="B76" s="7" t="n"/>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
-      <c r="K76" s="7" t="n"/>
-      <c r="L76" s="7" t="n"/>
-      <c r="M76" s="7" t="n"/>
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="n"/>
+      <c r="J76" s="6" t="n"/>
+      <c r="K76" s="6" t="n"/>
+      <c r="L76" s="6" t="n"/>
+      <c r="M76" s="6" t="n"/>
     </row>
     <row r="77">
-      <c r="D77" s="5" t="n"/>
+      <c r="D77" s="4" t="n"/>
     </row>
     <row r="78">
-      <c r="D78" s="5" t="n"/>
+      <c r="D78" s="4" t="n"/>
     </row>
     <row r="79">
-      <c r="D79" s="5" t="n"/>
+      <c r="D79" s="4" t="n"/>
     </row>
     <row r="80">
-      <c r="D80" s="5" t="n"/>
+      <c r="D80" s="4" t="n"/>
     </row>
     <row r="81">
-      <c r="D81" s="5" t="n"/>
+      <c r="D81" s="4" t="n"/>
     </row>
     <row r="82">
-      <c r="D82" s="5" t="n"/>
+      <c r="D82" s="4" t="n"/>
     </row>
     <row r="83">
-      <c r="D83" s="5" t="n"/>
+      <c r="D83" s="4" t="n"/>
     </row>
     <row r="84">
-      <c r="D84" s="5" t="n"/>
+      <c r="D84" s="4" t="n"/>
     </row>
     <row r="85">
-      <c r="D85" s="5" t="n"/>
+      <c r="D85" s="4" t="n"/>
     </row>
     <row r="86">
-      <c r="D86" s="5" t="n"/>
+      <c r="D86" s="4" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="5" t="n"/>
+      <c r="D87" s="4" t="n"/>
     </row>
     <row r="88">
-      <c r="D88" s="5" t="n"/>
+      <c r="D88" s="4" t="n"/>
     </row>
     <row r="89">
-      <c r="D89" s="5" t="n"/>
+      <c r="D89" s="4" t="n"/>
     </row>
     <row r="90">
-      <c r="D90" s="5" t="n"/>
+      <c r="D90" s="4" t="n"/>
     </row>
     <row r="91">
-      <c r="D91" s="6" t="n"/>
+      <c r="D91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="D92" s="5" t="n"/>
+      <c r="D92" s="4" t="n"/>
     </row>
     <row r="93">
-      <c r="D93" s="5" t="n"/>
+      <c r="D93" s="4" t="n"/>
     </row>
     <row r="94">
-      <c r="D94" s="5" t="n"/>
+      <c r="D94" s="4" t="n"/>
     </row>
     <row r="95">
-      <c r="D95" s="5" t="n"/>
+      <c r="D95" s="4" t="n"/>
     </row>
     <row r="100">
-      <c r="D100" s="5" t="n"/>
+      <c r="D100" s="4" t="n"/>
     </row>
     <row r="103">
-      <c r="D103" s="5" t="n"/>
+      <c r="D103" s="4" t="n"/>
     </row>
     <row r="104">
-      <c r="D104" s="5" t="n"/>
+      <c r="D104" s="4" t="n"/>
     </row>
     <row r="105">
-      <c r="D105" s="5" t="n"/>
+      <c r="D105" s="4" t="n"/>
     </row>
     <row r="106">
-      <c r="D106" s="5" t="n"/>
+      <c r="D106" s="4" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="5" t="n"/>
+      <c r="D107" s="4" t="n"/>
     </row>
     <row r="108">
-      <c r="D108" s="5" t="n"/>
+      <c r="D108" s="4" t="n"/>
     </row>
     <row r="110">
-      <c r="D110" s="5" t="n"/>
+      <c r="D110" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/compare_information.xlsx
+++ b/compare_information.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,6 +67,7 @@
     <font>
       <name val="等线"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
@@ -119,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -162,6 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -500,19 +502,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col width="14" customWidth="1" style="7" min="1" max="1"/>
-    <col width="24.625" customWidth="1" style="7" min="2" max="2"/>
-    <col width="33.375" customWidth="1" style="7" min="3" max="3"/>
-    <col width="21.5" customWidth="1" style="7" min="4" max="4"/>
-    <col width="23.625" customWidth="1" style="7" min="5" max="5"/>
-    <col width="27.25" customWidth="1" style="7" min="6" max="6"/>
-    <col width="18.625" customWidth="1" style="7" min="9" max="9"/>
+    <col width="14" customWidth="1" style="16" min="1" max="1"/>
+    <col width="24.625" customWidth="1" style="16" min="2" max="2"/>
+    <col width="33.375" customWidth="1" style="16" min="3" max="3"/>
+    <col width="21.5" customWidth="1" style="16" min="4" max="4"/>
+    <col width="23.625" customWidth="1" style="16" min="5" max="5"/>
+    <col width="27.25" customWidth="1" style="16" min="6" max="6"/>
+    <col width="18.625" customWidth="1" style="16" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="7">
+    <row r="1" ht="15.6" customHeight="1" s="16">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>IC</t>
@@ -529,7 +531,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.9" customHeight="1" s="7">
+    <row r="2" ht="13.9" customHeight="1" s="16">
       <c r="A2" s="2" t="n">
         <v>7272</v>
       </c>
@@ -544,7 +546,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="13.9" customHeight="1" s="7">
+    <row r="3" ht="13.9" customHeight="1" s="16">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>7202M</t>
@@ -1623,6 +1625,27 @@
       <c r="C93" t="inlineStr">
         <is>
           <t>BOE6.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MDT6.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HKC6.745 2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>HKC6.745 6-1</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1664,7 @@
   <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="10.5" customWidth="1" style="7" min="8" max="8"/>
+    <col width="10.5" customWidth="1" style="16" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2459,8 +2482,8 @@
   <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="11.125" customWidth="1" style="7" min="2" max="2"/>
-    <col width="13.625" customWidth="1" style="7" min="4" max="4"/>
+    <col width="11.125" customWidth="1" style="16" min="2" max="2"/>
+    <col width="13.625" customWidth="1" style="16" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
